--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0132.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0132.xlsx
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Ta chuẩn bị chiến đấu đây. Ngươi thì chuẩn bị ngủ đi.</t>
+          <t>Tao chuẩn bị chiến đấu đây. Mày thì chuẩn bị ngủ đi.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Ngươi còn cần Soliskin bảo vệ mà dám đứng đây làm như chuyện đó là bình thường à? Ngươi CỐ tình làm xấu mặt ta hả?</t>
+          <t>Mày còn cần Soliskin bảo vệ mà dám đứng đây làm như chuyện đó là bình thường à? Mày CỐ tình làm xấu mặt tao hả?</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>...Nhìn gì thế? Đừng có bảo xe của ta cũng biến mất luôn đấy!</t>
+          <t>...Nhìn gì thế? Đừng có bảo xe của tao cũng biến mất luôn đấy!</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Ngươi—ngươi—Ngươi! Ta còn dễ dạy bảo một con TARD-E hơn là dạy ngươi!</t>
+          <t>Mày—mày—MÀY! Tao còn dễ dạy bảo một con TARD-E hơn là dạy mày!</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Ta sẽ đuổi theo bọn chúng.</t>
+          <t>Tao sẽ đuổi theo bọn chúng.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Thật lòng. Ta còn biết nói gì với ngươi nữa? Suốt ngày chỉ biết quanh quẩn với tụi nó. Mồm mép không ngừng về tụi nó. THẾ MÀ Ngươi KHÔNG THEO DÕI CHÚT NÀO HẢ?!</t>
+          <t>Thật lòng. Tao còn biết nói gì với mày nữa? Suốt ngày chỉ biết quanh quẩn với tụi nó. Mồm mép không ngừng về tụi nó. THẾ MÀ MÀY KHÔNG THEO DÕI CHÚT NÀO HẢ?!</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Khóa xe lại khi rời đi! Khóa mỗi lần một! Ta phải nhắc ngươi bao nhiêu lần nữa hả?! Nhớ chưa?!</t>
+          <t>Khóa xe lại khi rời đi! Khóa mỗi lần một! Tao phải nhắc mày bao nhiêu lần nữa hả?! Nhớ chưa?!</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>"NHƯNG—Ta—KHÔNG—THỂ—DỪNG—LẠI!"</t>
+          <t>"NHƯNG—TAO—KHÔNG—THỂ—DỪNG—LẠI!"</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>"...Được rồi. Ta sẽ quay lại. Xin lỗi Giáo sư Lisandro và Dorien giùm ta nhé. Thí nghiệm thực địa khó khăn quá... Ta muốn trở về Rừng Bjartr."</t>
+          <t>"...Được rồi. Ta sẽ quay lại. Xin lỗi Giáo sư Lisandro và Dorien giùm ta nhé. Thí nghiệm thực địa khó khăn quá... Ta muốn trở về Bjartr Woods."</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Không đời nào! Ta không để một thằng Soliskin mạo hiểm đâu! Yêu cầu tăng viện từ trạm ngay, không bàn cãi!</t>
+          <t>Không đời nào! Tao không để một thằng Soliskin mạo hiểm đâu! Yêu cầu tăng viện từ trạm ngay, không bàn cãi!</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Ha! Dễ thương quá đi! Thư giãn đi, ta đùa thôi! Ta có ăn cắp đồ của ngươi đâu.</t>
+          <t>Ha! Dễ thương quá đi! Thư giãn đi, tao đùa thôi! Tao có ăn cắp đồ của mày đâu.</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Ôi, cái nhiệm vụ thu thập này sắp giết ta mất. Họ còn bắt lấy mẫu thực vật ở VÙNG NHIỄM ĐỘC NẶNG nữa chứ? Thật ác!</t>
+          <t>Ôi, cái nhiệm vụ thu thập này sắp giết tao mất. Họ còn bắt lấy mẫu thực vật ở VÙNG NHIỄM ĐỘC NẶNG nữa chứ? Thật ác!</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Ta không hiểu, nhóc à... Có gì đặc biệt ở đây không?</t>
+          <t>Tao không hiểu, nhóc à... Có gì đặc biệt ở đây không?</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Barton là Soliskin thông minh nhất mà ta từng gặp. Pelagia, đừng có gọi nó là đồ ngốc nữa!</t>
+          <t>Barton là Soliskin thông minh nhất mà tao từng gặp. Pelagia, đừng có gọi nó là đồ ngốc nữa!</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Góc nhìn của Barton à... Cậu nói đúng. Ta chưa bao giờ đặt mình vào vị trí của một Soliskin. Khi Barton tỉnh lại, ta sẽ xin lỗi nó!</t>
+          <t>Góc nhìn của Barton à... Cậu nói đúng. Tao chưa bao giờ đặt mình vào vị trí của một Soliskin. Khi Barton tỉnh lại, tao sẽ xin lỗi nó!</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Dễ như ăn bánh thôi. Để tụi ta lo!</t>
+          <t>Dễ như ăn bánh thôi. Để tụi tao lo!</t>
         </is>
       </c>
     </row>
@@ -27159,7 +27159,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>"Cuối cùng thì ta cũng tự do rồi! Cảm ơn cậu nhiều lắm!"</t>
+          <t>"Cuối cùng thì tao cũng tự do rồi! Cảm ơn cậu nhiều lắm!"</t>
         </is>
       </c>
     </row>
@@ -27484,7 +27484,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Thôi nào, đừng căng! Ta nghe rồi! Thằng nhỏ này đang cảm ơn cậu đấy.</t>
+          <t>Thôi nào, đừng căng! Tao nghe rồi! Thằng nhỏ này đang cảm ơn cậu đấy.</t>
         </is>
       </c>
     </row>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Ta chỉ thắc mắc không biết có kèm đồ ăn vặt không thôi...</t>
+          <t>Tao chỉ thắc mắc không biết có kèm đồ ăn vặt không thôi...</t>
         </is>
       </c>
     </row>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>THÍ NGHIỆM THÀNH CÔNG RỒI!!! Ta SẼ TỐT NGHIỆP ĐÚNG HẠN THẬT RỒI!!!</t>
+          <t>THÍ NGHIỆM THÀNH CÔNG RỒI!!! TAO SẼ TỐT NGHIỆP ĐÚNG HẠN THẬT RỒI!!!</t>
         </is>
       </c>
     </row>
